--- a/WBS.xlsx
+++ b/WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jun/GitStudy/human_A/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{377B396E-0980-2045-800F-0CA703711D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E61DCD9-4AED-7644-B6BA-0909E9690E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="자율주행 로봇 개발_WBS" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'자율주행 로봇 개발_WBS'!$K$1:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'자율주행 로봇 개발_WBS'!$K$1:$K$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'자율주행 로봇 개발_WBS'!$A$1:$BM$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'자율주행 로봇 개발_WBS'!$3:$5</definedName>
   </definedNames>
@@ -52,7 +52,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -61,7 +61,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="돋움"/>
             <family val="3"/>
             <charset val="129"/>
@@ -71,17 +71,36 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve"> Sum 100
-2. </t>
+</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
             <rFont val="돋움"/>
             <family val="3"/>
             <charset val="129"/>
@@ -91,7 +110,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -100,7 +119,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="돋움"/>
             <family val="3"/>
             <charset val="129"/>
@@ -110,7 +129,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -119,7 +138,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="돋움"/>
             <family val="3"/>
             <charset val="129"/>
@@ -129,7 +148,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -143,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="111">
   <si>
     <t>수행 Task</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -423,25 +442,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>N/A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 수집 명세서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최초 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ver 1.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>■ M2MCx 자율주행 로봇 개발 - WBS ('22년)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HumanIT - AI 기반의 양액 펌프 막힘 및 이상감지 원인 분류</t>
+  </si>
+  <si>
+    <t>김현준</t>
+  </si>
+  <si>
     <t>예정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최태민/
-최인구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최현석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획 및 요구사항 분석</t>
   </si>
   <si>
     <r>
@@ -450,11 +500,10 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>요구사항 분석</t>
+      <t>문제 정의 및 목표 수립</t>
     </r>
     <r>
       <rPr>
@@ -466,11 +515,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) 로봇 하드웨어 특성 분석
-  2) 작업환경 및 상용차/보조차량 작업 내용 분석
-  3) 로봇 센서 및 구동장치 성능 분석</t>
+  1) 양액 염분(화학적) 막힘 현상 타겟팅 및 주요 원인 분석
+  2) 예지보전(AutoEncoder 기반) 최종 목표 및 KPI 수립 (예: 막힘 징후 3일 전 탐지)
+  3) 전체 과제 일정 및 산출물 정의 </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -483,7 +531,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>시스템 구조 설계</t>
+      <t>스마트팜 도메인 환경 분석</t>
     </r>
     <r>
       <rPr>
@@ -495,11 +543,13 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) 로봇 시스템 통합 설계  
-  2) 로봇 동작 프로세스 설계
-  3) 아키텍처 검증 및 오류 분석</t>
+  1) 농가 온실 환경(온/습도, 광량) 및 양액 제어기 스펙 확인
+  2) 현장 센서(압력, 유량, EC, pH) 설치 위치 및 물리적 한계점 파악
+  3) 기존 농가의 세척(플러싱, 산처리) 주기 및 조치 이력 파악</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 수집 및 파이프라인 구축</t>
   </si>
   <si>
     <r>
@@ -512,7 +562,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>서버 구축 및 작업 환경 이미지/영상 데이터 수집</t>
+      <t>데이터 연동 및 수집</t>
     </r>
     <r>
       <rPr>
@@ -524,11 +574,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) Storage Server 구축 
-  2) 작업 환경 주요 발생 객체 데이터 수집
-  3) 도로 환경 데이터 수집</t>
+  1) 내부 통신(RS-485, Modbus 등) 기반 센서 원시 데이터(Raw data) 수집
+  2) 외부 환경 데이터(기상청 등) 필요시 연동
+  3) Storage Server(DB) 스키마 설계 및 데이터 적재 파이프라인 구축</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -541,7 +590,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ROS 프레임워크 개발(back-end)</t>
+      <t>데이터 정제 (Data Cleansing)</t>
     </r>
     <r>
       <rPr>
@@ -553,16 +602,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) ROS Master 생성 및 프로세스 기준 정보 표준화
-  2) TCPROS/UDPROS 기반 통신 모듈 개발 (내부 통신)
-  3) Nodelet API 셋팅
-  4) 센서, 액츄에이터, 네트워크 Driver Connection 모듈 개발
-  5) 클라이언트 라이브러리 함수 패키지 콜백 처리 모듈 개발 
-  6) ROS Launcher 개발
-  7) Job Scheduler 개발
-  8) SW 모듈화</t>
+  1) 센서 결측치 확인 및 도메인 기반 보간(Interpolation) 처리
+  2) 장비 오작동/노이즈로 인한 이상치(Outlier) 제거 룰셋 정의
+  3) 물리적 센서 캘리브레이션(영점 조절) 로그와 데이터 정합성 확인</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -575,7 +618,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>로봇 통합 테스트</t>
+      <t>파생 변수(Feature) 생성</t>
     </r>
     <r>
       <rPr>
@@ -587,21 +630,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) 성능평가를 위한 테스트베드 환경 구축
-  2) 자율주행 시나리오 별 테스트 수행
-  3) SW 기능 단위 테스트
-  4) 로봇 성능 테스트
-  5) 시스템 통합 테스트</t>
+  1) 유체 저항 지수 생성 (압력/유량 수식 적용)
+  2) 누적 염분 부하량 계산 (공급 EC와 배액 EC 차이 누적)
+  3) pH 불안정성 지수 산출 (침전 발생 임계점 6.5 초과 유지 시간 계산)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23년 실로봇 적용 계획 수립</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료 보고서 작성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -610,39 +642,10 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SW 관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  1) GIT 형상관리 시스템 구축
-  2) 최종 빌드 버전 업로드 및 다운로드</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SW 배포</t>
+      <t>정상 상태(Normal Baseline) 정의</t>
     </r>
     <r>
       <rPr>
@@ -654,18 +657,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) 22년 git 통한 개별 다운로드 및 빌드 
-  2) 23년 클라우드 기반 SW 배포 시스템 구축</t>
+  1) 배관/점적 핀 신규 교체 및 세척 직후의 '정상(Normal)' 데이터 구간 추출
+  2) 시간대별/생육기별 정상 패턴 군집화
+  3) 센서 캘리브레이션 로그 확인</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료 보고서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 결과 보고서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -678,175 +673,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>테스트 및 SW 배포 계획 수립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  1) 성능평가를 위한 테스트베드 구축 계획 수립
-  2) 자율주행 시나리오 別 테스트 계획 수립
-  3) SW 배포 프로세스 계획 수립</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터 수집</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>개발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SW 관리 및 배포</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>과제 계획서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SW Build Package</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터 수집 명세서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전개 계획서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데모 영상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작성자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>버전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최초 작성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ver 1.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>■ M2MCx 자율주행 로봇 개발 - WBS ('22년)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최현석/
-최인구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최인구/
-최현석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1차 시나리오 별 자율주행 데모 시연</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  1) 외부 시스템에서 로봇 작업 지시와 목적지까지의 자율주행 모드 시연
-  2) 자율주행 中 장애물 인식 및 회피 모드 시연</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시스템 설계도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HumanIT - AI 기반의 양액 펌프 막힘 및 이상감지 원인 분류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요구사항 검토
-  1) 관련 연구, 문헌 조사 및 전문가 자문을 통한 핵심 원천 기술 동향 검토
-  2) 자율주행 로봇 개발을 위한 필요기술 검토
-  3) RFP 자료 검토 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>문제 정의</t>
+      <t>검증 및 임계점(Threshold) 설정</t>
     </r>
     <r>
       <rPr>
@@ -858,19 +685,57 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-  1) 로봇 작업 시나리오 정의
-  2) 과제 개발범위 및 최종목표 수립
-  3) 과제일정 수립</t>
+  1) 가짜(막힘 모사) 실데이터 주입을 통한 이상 감지 테스트
+  2) 오알람(False Alarm)을 최소화하는 최적의 알람 임계점 설정</t>
     </r>
   </si>
   <si>
-    <t>김현준</t>
-  </si>
-  <si>
-    <t>분석 주제 선정</t>
-  </si>
-  <si>
-    <t>기획 및 설계</t>
+    <t>시스템 개발</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDA 및 데이터 전처리 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가설 설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  1) 정상 데이터를 활용한 AutoEncoder 아키텍처 설계
+  2) 시계열 특성을 반영한 재구성 오차(Reconstruction Error) 학습</t>
+    </r>
+  </si>
+  <si>
+    <t>데이터 분석 및 모델링</t>
+  </si>
+  <si>
+    <t>모델생성
+  1) 
+  2) 오알람(False Alarm)을 최소화하는 최적의 알람 임계점 설정</t>
+  </si>
+  <si>
+    <t>모델검증
+  1) 
+  2) 오알람(False Alarm)을 최소화하는 최적의 알람 임계점 설정</t>
+  </si>
+  <si>
+    <t>전처리 주피터노트북</t>
   </si>
 </sst>
 </file>
@@ -910,7 +775,7 @@
     <numFmt numFmtId="193" formatCode="mm&quot;월&quot;\ &quot;26일&quot;"/>
     <numFmt numFmtId="194" formatCode="mm&quot;월&quot;\ &quot;12일&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,25 +908,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color indexed="81"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="81"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1661,7 +1549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1779,7 +1667,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2025,25 +1913,37 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2109,30 +2009,30 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="26">
     <dxf>
       <font>
         <color theme="4" tint="0.39994506668294322"/>
@@ -2155,61 +2055,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="9" tint="0.79998168889431442"/>
+        <color theme="4" tint="0.39994506668294322"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="0.79998168889431442"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2220,6 +2070,26 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.79998168889431442"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.79998168889431442"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2265,6 +2135,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="4" tint="0.79998168889431442"/>
       </font>
       <fill>
@@ -2295,6 +2175,76 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="0.79998168889431442"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="0.79998168889431442"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="9" tint="0.79998168889431442"/>
       </font>
       <fill>
@@ -2310,16 +2260,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2656,10 +2596,10 @@
         <v>50</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -2670,13 +2610,13 @@
         <v>44726</v>
       </c>
       <c r="D5" s="119" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E5" s="119" t="s">
         <v>80</v>
       </c>
       <c r="F5" s="118" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -3102,7 +3042,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BN34"/>
+  <dimension ref="A1:BN39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -3124,10 +3064,10 @@
   <sheetData>
     <row r="1" spans="1:66" ht="16">
       <c r="A1" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="128"/>
-      <c r="I1" s="129"/>
+        <v>91</v>
+      </c>
+      <c r="H1" s="132"/>
+      <c r="I1" s="133"/>
       <c r="J1" s="17" t="s">
         <v>76</v>
       </c>
@@ -3142,187 +3082,187 @@
     </row>
     <row r="3" spans="1:66" ht="16.5" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="133" t="s">
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="137" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="134"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="146" t="s">
+      <c r="H3" s="138"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="149" t="s">
+      <c r="K3" s="125" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="M3" s="152" t="s">
+      <c r="M3" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="125"/>
-      <c r="S3" s="125"/>
-      <c r="T3" s="125"/>
-      <c r="U3" s="125"/>
-      <c r="V3" s="125"/>
-      <c r="W3" s="125"/>
-      <c r="X3" s="125"/>
-      <c r="Y3" s="125"/>
-      <c r="Z3" s="125"/>
-      <c r="AA3" s="125"/>
-      <c r="AB3" s="125"/>
-      <c r="AC3" s="125"/>
-      <c r="AD3" s="125"/>
-      <c r="AE3" s="125"/>
-      <c r="AF3" s="125"/>
-      <c r="AG3" s="125"/>
-      <c r="AH3" s="125"/>
-      <c r="AI3" s="125"/>
-      <c r="AJ3" s="125"/>
-      <c r="AK3" s="125"/>
-      <c r="AL3" s="125"/>
-      <c r="AM3" s="125"/>
-      <c r="AN3" s="125"/>
-      <c r="AO3" s="125"/>
-      <c r="AP3" s="125"/>
-      <c r="AQ3" s="125"/>
-      <c r="AR3" s="125"/>
-      <c r="AS3" s="125"/>
-      <c r="AT3" s="125"/>
-      <c r="AU3" s="125"/>
-      <c r="AV3" s="125"/>
-      <c r="AW3" s="125"/>
-      <c r="AX3" s="125"/>
-      <c r="AY3" s="125"/>
-      <c r="AZ3" s="125"/>
-      <c r="BA3" s="125"/>
-      <c r="BB3" s="125"/>
-      <c r="BC3" s="125"/>
-      <c r="BD3" s="125"/>
-      <c r="BE3" s="125"/>
-      <c r="BF3" s="125"/>
-      <c r="BG3" s="125"/>
-      <c r="BH3" s="125"/>
-      <c r="BI3" s="125"/>
-      <c r="BJ3" s="125"/>
-      <c r="BK3" s="125"/>
-      <c r="BL3" s="125"/>
-      <c r="BM3" s="126"/>
-      <c r="BN3" s="121" t="s">
+      <c r="N3" s="156"/>
+      <c r="O3" s="156"/>
+      <c r="P3" s="156"/>
+      <c r="Q3" s="156"/>
+      <c r="R3" s="156"/>
+      <c r="S3" s="156"/>
+      <c r="T3" s="156"/>
+      <c r="U3" s="156"/>
+      <c r="V3" s="156"/>
+      <c r="W3" s="156"/>
+      <c r="X3" s="156"/>
+      <c r="Y3" s="156"/>
+      <c r="Z3" s="156"/>
+      <c r="AA3" s="156"/>
+      <c r="AB3" s="156"/>
+      <c r="AC3" s="156"/>
+      <c r="AD3" s="156"/>
+      <c r="AE3" s="156"/>
+      <c r="AF3" s="156"/>
+      <c r="AG3" s="156"/>
+      <c r="AH3" s="156"/>
+      <c r="AI3" s="156"/>
+      <c r="AJ3" s="156"/>
+      <c r="AK3" s="156"/>
+      <c r="AL3" s="156"/>
+      <c r="AM3" s="156"/>
+      <c r="AN3" s="156"/>
+      <c r="AO3" s="156"/>
+      <c r="AP3" s="156"/>
+      <c r="AQ3" s="156"/>
+      <c r="AR3" s="156"/>
+      <c r="AS3" s="156"/>
+      <c r="AT3" s="156"/>
+      <c r="AU3" s="156"/>
+      <c r="AV3" s="156"/>
+      <c r="AW3" s="156"/>
+      <c r="AX3" s="156"/>
+      <c r="AY3" s="156"/>
+      <c r="AZ3" s="156"/>
+      <c r="BA3" s="156"/>
+      <c r="BB3" s="156"/>
+      <c r="BC3" s="156"/>
+      <c r="BD3" s="156"/>
+      <c r="BE3" s="156"/>
+      <c r="BF3" s="156"/>
+      <c r="BG3" s="156"/>
+      <c r="BH3" s="156"/>
+      <c r="BI3" s="156"/>
+      <c r="BJ3" s="156"/>
+      <c r="BK3" s="156"/>
+      <c r="BL3" s="156"/>
+      <c r="BM3" s="157"/>
+      <c r="BN3" s="153" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:66" ht="16.5" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="153"/>
-      <c r="M4" s="153"/>
-      <c r="N4" s="124" t="s">
+      <c r="B4" s="135"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="131" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124" t="s">
+      <c r="O4" s="131"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="124" t="s">
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="131"/>
+      <c r="V4" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="124"/>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="124"/>
-      <c r="AA4" s="124" t="s">
+      <c r="W4" s="131"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="131" t="s">
         <v>73</v>
       </c>
-      <c r="AB4" s="124"/>
-      <c r="AC4" s="124"/>
-      <c r="AD4" s="124"/>
-      <c r="AE4" s="124" t="s">
+      <c r="AB4" s="131"/>
+      <c r="AC4" s="131"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131" t="s">
         <v>56</v>
       </c>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="124" t="s">
+      <c r="AF4" s="131"/>
+      <c r="AG4" s="131"/>
+      <c r="AH4" s="131"/>
+      <c r="AI4" s="131"/>
+      <c r="AJ4" s="131" t="s">
         <v>79</v>
       </c>
-      <c r="AK4" s="124"/>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124" t="s">
+      <c r="AK4" s="131"/>
+      <c r="AL4" s="131"/>
+      <c r="AM4" s="131"/>
+      <c r="AN4" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="AO4" s="124"/>
-      <c r="AP4" s="124"/>
-      <c r="AQ4" s="124"/>
-      <c r="AR4" s="127" t="s">
+      <c r="AO4" s="131"/>
+      <c r="AP4" s="131"/>
+      <c r="AQ4" s="131"/>
+      <c r="AR4" s="158" t="s">
         <v>57</v>
       </c>
-      <c r="AS4" s="127"/>
-      <c r="AT4" s="127"/>
-      <c r="AU4" s="127"/>
-      <c r="AV4" s="127"/>
-      <c r="AW4" s="124" t="s">
-        <v>113</v>
-      </c>
-      <c r="AX4" s="124"/>
-      <c r="AY4" s="124"/>
-      <c r="AZ4" s="124"/>
-      <c r="BA4" s="124" t="s">
+      <c r="AS4" s="158"/>
+      <c r="AT4" s="158"/>
+      <c r="AU4" s="158"/>
+      <c r="AV4" s="158"/>
+      <c r="AW4" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX4" s="131"/>
+      <c r="AY4" s="131"/>
+      <c r="AZ4" s="131"/>
+      <c r="BA4" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="BB4" s="124"/>
-      <c r="BC4" s="124"/>
-      <c r="BD4" s="124"/>
-      <c r="BE4" s="127" t="s">
+      <c r="BB4" s="131"/>
+      <c r="BC4" s="131"/>
+      <c r="BD4" s="131"/>
+      <c r="BE4" s="158" t="s">
         <v>53</v>
       </c>
-      <c r="BF4" s="127"/>
-      <c r="BG4" s="127"/>
-      <c r="BH4" s="127"/>
-      <c r="BI4" s="127"/>
-      <c r="BJ4" s="124" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK4" s="124"/>
-      <c r="BL4" s="124"/>
-      <c r="BM4" s="124"/>
-      <c r="BN4" s="122"/>
+      <c r="BF4" s="158"/>
+      <c r="BG4" s="158"/>
+      <c r="BH4" s="158"/>
+      <c r="BI4" s="158"/>
+      <c r="BJ4" s="131" t="s">
+        <v>86</v>
+      </c>
+      <c r="BK4" s="131"/>
+      <c r="BL4" s="131"/>
+      <c r="BM4" s="131"/>
+      <c r="BN4" s="154"/>
     </row>
     <row r="5" spans="1:66" ht="30">
       <c r="A5" s="2"/>
-      <c r="B5" s="132"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="141"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="145"/>
       <c r="G5" s="19" t="s">
         <v>44</v>
       </c>
@@ -3332,10 +3272,10 @@
       <c r="I5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="148"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="154"/>
-      <c r="M5" s="154"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
       <c r="N5" s="91" t="s">
         <v>58</v>
       </c>
@@ -3492,12 +3432,12 @@
       <c r="BM5" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="BN5" s="123"/>
+      <c r="BN5" s="155"/>
     </row>
     <row r="6" spans="1:66" ht="30.5" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="39" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="20"/>
@@ -3514,12 +3454,12 @@
         <v>13</v>
       </c>
       <c r="J6" s="24">
-        <f>(SUMIF(J7:J23,"완료",K7:K23)+(SUMIF(J7:J23,"진행중",K7:K23)/2)+(SUMIF(J7:J23,"지연중",K7:K23)/2))/SUM(K7:K23)</f>
-        <v>0</v>
+        <f>(SUMIF(J7:J28,"완료",K7:K28)+(SUMIF(J7:J28,"진행중",K7:K28)/2)+(SUMIF(J7:J28,"지연중",K7:K28)/2))/SUM(K7:K28)</f>
+        <v>0.36046511627906974</v>
       </c>
       <c r="K6" s="25">
-        <f>SUM(K7:K27)</f>
-        <v>37</v>
+        <f>SUM(K7:K32)</f>
+        <v>43</v>
       </c>
       <c r="L6" s="26"/>
       <c r="M6" s="46"/>
@@ -3688,19 +3628,19 @@
         <v>1</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="E7" s="41"/>
       <c r="F7" s="29"/>
       <c r="G7" s="30">
-        <v>44622</v>
+        <v>46119</v>
       </c>
       <c r="H7" s="30">
-        <v>44712</v>
+        <v>46121</v>
       </c>
       <c r="I7" s="31">
         <f t="shared" ref="I7:I9" si="0">NETWORKDAYS(G7,H7)</f>
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="J7" s="32"/>
       <c r="K7" s="33"/>
@@ -3872,30 +3812,30 @@
       <c r="E8" s="42">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>126</v>
+      <c r="F8" s="123" t="s">
+        <v>96</v>
       </c>
       <c r="G8" s="52">
-        <v>44622</v>
+        <v>46119</v>
       </c>
       <c r="H8" s="52">
-        <v>44651</v>
+        <v>46119</v>
       </c>
       <c r="I8" s="53">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K8" s="54">
         <v>1</v>
       </c>
       <c r="L8" s="58" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="N8" s="5">
         <v>44564</v>
@@ -4064,29 +4004,29 @@
         <v>1.2</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G9" s="52">
-        <v>44652</v>
+        <v>46119</v>
       </c>
       <c r="H9" s="52">
-        <v>44691</v>
+        <v>46119</v>
       </c>
       <c r="I9" s="53">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K9" s="54">
         <v>2</v>
       </c>
       <c r="L9" s="58" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="N9" s="5">
         <v>44564</v>
@@ -4246,35 +4186,31 @@
       </c>
       <c r="BN9" s="11"/>
     </row>
-    <row r="10" spans="1:66" ht="71" customHeight="1">
-      <c r="E10" s="42">
-        <v>1.3</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="52">
-        <v>44652</v>
-      </c>
-      <c r="H10" s="52">
-        <v>44691</v>
-      </c>
-      <c r="I10" s="53">
-        <f t="shared" ref="I10" si="1">NETWORKDAYS(G10,H10)</f>
-        <v>28</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="54">
+    <row r="10" spans="1:66" ht="15.5" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="40">
         <v>2</v>
       </c>
-      <c r="L10" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="M10" s="58" t="s">
-        <v>128</v>
-      </c>
+      <c r="D10" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="41"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30">
+        <v>46121</v>
+      </c>
+      <c r="H10" s="30">
+        <v>46121</v>
+      </c>
+      <c r="I10" s="56">
+        <f>NETWORKDAYS(G10,H10)</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="50"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="59"/>
       <c r="N10" s="5">
         <v>44564</v>
       </c>
@@ -4433,38 +4369,34 @@
       </c>
       <c r="BN10" s="11"/>
     </row>
-    <row r="11" spans="1:66" ht="68" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="42">
-        <v>1.4</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>98</v>
+    <row r="11" spans="1:66" ht="69" customHeight="1">
+      <c r="E11" s="62">
+        <v>2.1</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>99</v>
       </c>
       <c r="G11" s="52">
-        <v>44692</v>
+        <v>46119</v>
       </c>
       <c r="H11" s="52">
-        <v>44732</v>
-      </c>
-      <c r="I11" s="53">
-        <f>NETWORKDAYS(G11,H11)</f>
-        <v>29</v>
+        <v>46119</v>
+      </c>
+      <c r="I11" s="47">
+        <f t="shared" ref="I11" si="1">NETWORKDAYS(G11,H11)</f>
+        <v>1</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="54">
-        <v>2</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>107</v>
+        <v>81</v>
+      </c>
+      <c r="K11" s="48">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="N11" s="5">
         <v>44564</v>
@@ -4628,22 +4560,22 @@
       <c r="A12" s="2"/>
       <c r="B12" s="27"/>
       <c r="C12" s="40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E12" s="41"/>
       <c r="F12" s="29"/>
-      <c r="G12" s="55">
-        <v>44719</v>
-      </c>
-      <c r="H12" s="55">
-        <v>44764</v>
+      <c r="G12" s="30">
+        <v>46122</v>
+      </c>
+      <c r="H12" s="30">
+        <v>46122</v>
       </c>
       <c r="I12" s="56">
         <f>NETWORKDAYS(G12,H12)</f>
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J12" s="50"/>
       <c r="K12" s="57"/>
@@ -4807,34 +4739,34 @@
       </c>
       <c r="BN12" s="11"/>
     </row>
-    <row r="13" spans="1:66" ht="70.25" customHeight="1">
-      <c r="E13" s="42">
-        <v>2.1</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>88</v>
+    <row r="13" spans="1:66" ht="69" customHeight="1">
+      <c r="E13" s="62">
+        <v>3.1</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>100</v>
       </c>
       <c r="G13" s="52">
-        <v>44719</v>
+        <v>46119</v>
       </c>
       <c r="H13" s="52">
-        <v>44727</v>
-      </c>
-      <c r="I13" s="53">
-        <f t="shared" ref="I13" si="2">NETWORKDAYS(G13,H13)</f>
-        <v>7</v>
+        <v>46122</v>
+      </c>
+      <c r="I13" s="47">
+        <f t="shared" ref="I13:I14" si="2">NETWORKDAYS(G13,H13)</f>
+        <v>4</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="54">
-        <v>3</v>
-      </c>
-      <c r="L13" s="58" t="s">
-        <v>124</v>
+        <v>67</v>
+      </c>
+      <c r="K13" s="48">
+        <v>5</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="M13" s="58" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="N13" s="5">
         <v>44564</v>
@@ -4994,31 +4926,35 @@
       </c>
       <c r="BN13" s="11"/>
     </row>
-    <row r="14" spans="1:66" ht="15.5" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="40">
-        <v>3</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="55">
-        <v>44746</v>
-      </c>
-      <c r="H14" s="55">
-        <v>44771</v>
-      </c>
-      <c r="I14" s="56">
-        <f>NETWORKDAYS(G14,H14)</f>
-        <v>20</v>
-      </c>
-      <c r="J14" s="50"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
+    <row r="14" spans="1:66" ht="69" customHeight="1">
+      <c r="E14" s="62">
+        <v>3.2</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="52">
+        <v>46119</v>
+      </c>
+      <c r="H14" s="52">
+        <v>46122</v>
+      </c>
+      <c r="I14" s="47">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="48">
+        <v>5</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" s="58" t="s">
+        <v>93</v>
+      </c>
       <c r="N14" s="5">
         <v>44564</v>
       </c>
@@ -5179,32 +5115,32 @@
     </row>
     <row r="15" spans="1:66" ht="69" customHeight="1">
       <c r="E15" s="62">
-        <v>3.1</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>89</v>
+        <v>3.3</v>
+      </c>
+      <c r="F15" s="124" t="s">
+        <v>102</v>
       </c>
       <c r="G15" s="52">
-        <v>44746</v>
+        <v>46119</v>
       </c>
       <c r="H15" s="52">
-        <v>44762</v>
+        <v>46122</v>
       </c>
       <c r="I15" s="47">
         <f t="shared" ref="I15" si="3">NETWORKDAYS(G15,H15)</f>
-        <v>13</v>
-      </c>
-      <c r="J15" s="47" t="s">
-        <v>77</v>
+        <v>4</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>67</v>
       </c>
       <c r="K15" s="48">
         <v>5</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="M15" s="60" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="M15" s="58" t="s">
+        <v>93</v>
       </c>
       <c r="N15" s="5">
         <v>44564</v>
@@ -5368,22 +5304,22 @@
       <c r="A16" s="2"/>
       <c r="B16" s="27"/>
       <c r="C16" s="40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="29"/>
-      <c r="G16" s="55">
-        <v>44774</v>
-      </c>
-      <c r="H16" s="55">
-        <v>44895</v>
+      <c r="G16" s="30">
+        <v>46121</v>
+      </c>
+      <c r="H16" s="30">
+        <v>46121</v>
       </c>
       <c r="I16" s="56">
         <f>NETWORKDAYS(G16,H16)</f>
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="J16" s="50"/>
       <c r="K16" s="57"/>
@@ -5547,783 +5483,358 @@
       </c>
       <c r="BN16" s="11"/>
     </row>
-    <row r="17" spans="1:66" ht="155" customHeight="1">
+    <row r="17" spans="1:66" ht="69" customHeight="1">
       <c r="E17" s="62">
         <v>4.0999999999999996</v>
       </c>
-      <c r="F17" s="63" t="s">
-        <v>90</v>
+      <c r="F17" s="124" t="s">
+        <v>106</v>
       </c>
       <c r="G17" s="52">
-        <v>44753</v>
-      </c>
-      <c r="H17" s="52">
-        <v>44772</v>
+        <v>46117</v>
+      </c>
+      <c r="H17" s="121">
+        <v>46123</v>
       </c>
       <c r="I17" s="47">
-        <f t="shared" ref="I17" si="4">NETWORKDAYS(G17,H17)</f>
-        <v>15</v>
+        <f t="shared" ref="I17:I19" si="4">NETWORKDAYS(G17,H17)</f>
+        <v>5</v>
       </c>
       <c r="J17" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="48">
+        <v>5</v>
+      </c>
+      <c r="M17" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="68"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="68"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="72"/>
+      <c r="AB17" s="73"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="77"/>
+      <c r="AG17" s="78"/>
+      <c r="AH17" s="79"/>
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="83"/>
+      <c r="AN17" s="72"/>
+      <c r="AO17" s="73"/>
+      <c r="AP17" s="74"/>
+      <c r="AQ17" s="94"/>
+      <c r="AR17" s="95"/>
+      <c r="AS17" s="84"/>
+      <c r="AT17" s="85"/>
+      <c r="AU17" s="96"/>
+      <c r="AV17" s="106"/>
+      <c r="AW17" s="86"/>
+      <c r="AX17" s="5"/>
+      <c r="AY17" s="87"/>
+      <c r="AZ17" s="88"/>
+      <c r="BA17" s="8"/>
+      <c r="BB17" s="5"/>
+      <c r="BC17" s="65"/>
+      <c r="BD17" s="109"/>
+      <c r="BE17" s="111"/>
+      <c r="BF17" s="67"/>
+      <c r="BG17" s="68"/>
+      <c r="BH17" s="108"/>
+      <c r="BI17" s="112"/>
+      <c r="BJ17" s="86"/>
+      <c r="BK17" s="89"/>
+      <c r="BL17" s="87"/>
+      <c r="BM17" s="90"/>
+      <c r="BN17" s="11"/>
+    </row>
+    <row r="18" spans="1:66" ht="69" customHeight="1">
+      <c r="E18" s="62">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="52">
+        <v>46118</v>
+      </c>
+      <c r="H18" s="121">
+        <v>46124</v>
+      </c>
+      <c r="I18" s="47">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J18" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="K17" s="48">
-        <v>10</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="K18" s="48">
+        <v>5</v>
+      </c>
+      <c r="M18" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="68"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="72"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="74"/>
+      <c r="AD18" s="75"/>
+      <c r="AE18" s="76"/>
+      <c r="AF18" s="77"/>
+      <c r="AG18" s="78"/>
+      <c r="AH18" s="79"/>
+      <c r="AI18" s="80"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="81"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="83"/>
+      <c r="AN18" s="72"/>
+      <c r="AO18" s="73"/>
+      <c r="AP18" s="74"/>
+      <c r="AQ18" s="94"/>
+      <c r="AR18" s="95"/>
+      <c r="AS18" s="84"/>
+      <c r="AT18" s="85"/>
+      <c r="AU18" s="96"/>
+      <c r="AV18" s="106"/>
+      <c r="AW18" s="86"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="87"/>
+      <c r="AZ18" s="88"/>
+      <c r="BA18" s="8"/>
+      <c r="BB18" s="5"/>
+      <c r="BC18" s="65"/>
+      <c r="BD18" s="109"/>
+      <c r="BE18" s="111"/>
+      <c r="BF18" s="67"/>
+      <c r="BG18" s="68"/>
+      <c r="BH18" s="108"/>
+      <c r="BI18" s="112"/>
+      <c r="BJ18" s="86"/>
+      <c r="BK18" s="89"/>
+      <c r="BL18" s="87"/>
+      <c r="BM18" s="90"/>
+      <c r="BN18" s="11"/>
+    </row>
+    <row r="19" spans="1:66" ht="69" customHeight="1">
+      <c r="E19" s="62">
+        <v>4.3</v>
+      </c>
+      <c r="F19" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="M17" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="N17" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O17" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P17" s="5">
-        <v>44579</v>
-      </c>
-      <c r="Q17" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R17" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S17" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T17" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U17" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V17" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W17" s="5">
-        <v>44628</v>
-      </c>
-      <c r="X17" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y17" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z17" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA17" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB17" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC17" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD17" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE17" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF17" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG17" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH17" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI17" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ17" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK17" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL17" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM17" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN17" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO17" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP17" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ17" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR17" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS17" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT17" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU17" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV17" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW17" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX17" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY17" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ17" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA17" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB17" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC17" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD17" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE17" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF17" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG17" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH17" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI17" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ17" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK17" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL17" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM17" s="90">
-        <v>44922</v>
-      </c>
-      <c r="BN17" s="11"/>
-    </row>
-    <row r="18" spans="1:66" ht="15.5" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="40">
+      <c r="G19" s="52">
+        <v>46119</v>
+      </c>
+      <c r="H19" s="121">
+        <v>46125</v>
+      </c>
+      <c r="I19" s="47">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="55">
-        <v>44896</v>
-      </c>
-      <c r="H18" s="55">
-        <v>44911</v>
-      </c>
-      <c r="I18" s="56">
-        <f>NETWORKDAYS(G18,H18)</f>
-        <v>12</v>
-      </c>
-      <c r="J18" s="50"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O18" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P18" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q18" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R18" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S18" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T18" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U18" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V18" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W18" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X18" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y18" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z18" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA18" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB18" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC18" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD18" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE18" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF18" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG18" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH18" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI18" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ18" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK18" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL18" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM18" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN18" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO18" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP18" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ18" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR18" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS18" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT18" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU18" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV18" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW18" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX18" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY18" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ18" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA18" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB18" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC18" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD18" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE18" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF18" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG18" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH18" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI18" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ18" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK18" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL18" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM18" s="90">
-        <v>44922</v>
-      </c>
-      <c r="BN18" s="11"/>
-    </row>
-    <row r="19" spans="1:66" ht="102.5" customHeight="1">
-      <c r="E19" s="62">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="52">
-        <v>44855</v>
-      </c>
-      <c r="H19" s="52">
-        <v>44862</v>
-      </c>
-      <c r="I19" s="47"/>
       <c r="J19" s="47" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K19" s="48">
-        <v>2</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="N19" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O19" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P19" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q19" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R19" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S19" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T19" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U19" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V19" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W19" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X19" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y19" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z19" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA19" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB19" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC19" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD19" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE19" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF19" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG19" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH19" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI19" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ19" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK19" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL19" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM19" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN19" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO19" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP19" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ19" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR19" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS19" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT19" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU19" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV19" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW19" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX19" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY19" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ19" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA19" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB19" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC19" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD19" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE19" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF19" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG19" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH19" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI19" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ19" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK19" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL19" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM19" s="90">
-        <v>44922</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M19" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="68"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="68"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="71"/>
+      <c r="AA19" s="72"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="75"/>
+      <c r="AE19" s="76"/>
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="78"/>
+      <c r="AH19" s="79"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="81"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="83"/>
+      <c r="AN19" s="72"/>
+      <c r="AO19" s="73"/>
+      <c r="AP19" s="74"/>
+      <c r="AQ19" s="94"/>
+      <c r="AR19" s="95"/>
+      <c r="AS19" s="84"/>
+      <c r="AT19" s="85"/>
+      <c r="AU19" s="96"/>
+      <c r="AV19" s="106"/>
+      <c r="AW19" s="86"/>
+      <c r="AX19" s="5"/>
+      <c r="AY19" s="87"/>
+      <c r="AZ19" s="88"/>
+      <c r="BA19" s="8"/>
+      <c r="BB19" s="5"/>
+      <c r="BC19" s="65"/>
+      <c r="BD19" s="109"/>
+      <c r="BE19" s="111"/>
+      <c r="BF19" s="67"/>
+      <c r="BG19" s="68"/>
+      <c r="BH19" s="108"/>
+      <c r="BI19" s="112"/>
+      <c r="BJ19" s="86"/>
+      <c r="BK19" s="89"/>
+      <c r="BL19" s="87"/>
+      <c r="BM19" s="90"/>
       <c r="BN19" s="11"/>
     </row>
-    <row r="20" spans="1:66" ht="15.5" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="40">
-        <v>6</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="55">
-        <v>44914</v>
-      </c>
-      <c r="H20" s="55">
-        <v>44918</v>
-      </c>
-      <c r="I20" s="56">
-        <f>NETWORKDAYS(G20,H20)</f>
+    <row r="20" spans="1:66" ht="69" customHeight="1">
+      <c r="E20" s="62">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F20" s="122" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="52">
+        <v>46119</v>
+      </c>
+      <c r="H20" s="121">
+        <v>46125</v>
+      </c>
+      <c r="I20" s="47">
+        <f t="shared" ref="I20" si="5">NETWORKDAYS(G20,H20)</f>
         <v>5</v>
       </c>
-      <c r="J20" s="50"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O20" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P20" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q20" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R20" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S20" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T20" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U20" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V20" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W20" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X20" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y20" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z20" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA20" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB20" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC20" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD20" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE20" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF20" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG20" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH20" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI20" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ20" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK20" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL20" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM20" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN20" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO20" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP20" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ20" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR20" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS20" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT20" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU20" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV20" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW20" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX20" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY20" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ20" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA20" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB20" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC20" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD20" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE20" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF20" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG20" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH20" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI20" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ20" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK20" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL20" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM20" s="90">
-        <v>44922</v>
-      </c>
+      <c r="J20" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="48">
+        <v>5</v>
+      </c>
+      <c r="M20" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="71"/>
+      <c r="AA20" s="72"/>
+      <c r="AB20" s="73"/>
+      <c r="AC20" s="74"/>
+      <c r="AD20" s="75"/>
+      <c r="AE20" s="76"/>
+      <c r="AF20" s="77"/>
+      <c r="AG20" s="78"/>
+      <c r="AH20" s="79"/>
+      <c r="AI20" s="80"/>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="81"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="72"/>
+      <c r="AO20" s="73"/>
+      <c r="AP20" s="74"/>
+      <c r="AQ20" s="94"/>
+      <c r="AR20" s="95"/>
+      <c r="AS20" s="84"/>
+      <c r="AT20" s="85"/>
+      <c r="AU20" s="96"/>
+      <c r="AV20" s="106"/>
+      <c r="AW20" s="86"/>
+      <c r="AX20" s="5"/>
+      <c r="AY20" s="87"/>
+      <c r="AZ20" s="88"/>
+      <c r="BA20" s="8"/>
+      <c r="BB20" s="5"/>
+      <c r="BC20" s="65"/>
+      <c r="BD20" s="109"/>
+      <c r="BE20" s="111"/>
+      <c r="BF20" s="67"/>
+      <c r="BG20" s="68"/>
+      <c r="BH20" s="108"/>
+      <c r="BI20" s="112"/>
+      <c r="BJ20" s="86"/>
+      <c r="BK20" s="89"/>
+      <c r="BL20" s="87"/>
+      <c r="BM20" s="90"/>
       <c r="BN20" s="11"/>
     </row>
-    <row r="21" spans="1:66" ht="63" customHeight="1">
+    <row r="21" spans="1:66" ht="15.5" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="42">
-        <v>6.1</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="52">
-        <v>44865</v>
-      </c>
-      <c r="H21" s="52">
-        <v>44865</v>
-      </c>
-      <c r="I21" s="53">
-        <f t="shared" ref="I21" si="5">NETWORKDAYS(G21,H21)</f>
+      <c r="B21" s="27"/>
+      <c r="C21" s="40">
+        <v>5</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="41"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="30">
+        <v>46121</v>
+      </c>
+      <c r="H21" s="30">
+        <v>46121</v>
+      </c>
+      <c r="I21" s="56">
+        <f>NETWORKDAYS(G21,H21)</f>
         <v>1</v>
       </c>
-      <c r="J21" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="K21" s="54">
-        <v>2</v>
-      </c>
-      <c r="L21" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="58" t="s">
-        <v>85</v>
-      </c>
+      <c r="J21" s="50"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
       <c r="N21" s="5">
         <v>44564</v>
       </c>
       <c r="O21" s="64">
         <v>44572</v>
       </c>
-      <c r="P21" s="65">
+      <c r="P21" s="5">
         <v>44579</v>
       </c>
       <c r="Q21" s="66">
@@ -6344,7 +5855,7 @@
       <c r="V21" s="5">
         <v>44621</v>
       </c>
-      <c r="W21" s="67">
+      <c r="W21" s="5">
         <v>44628</v>
       </c>
       <c r="X21" s="68">
@@ -6475,1161 +5986,869 @@
       </c>
       <c r="BN21" s="11"/>
     </row>
-    <row r="22" spans="1:66" ht="15.5" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="40">
-        <v>7</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="55">
-        <v>44911</v>
-      </c>
-      <c r="H22" s="55">
-        <v>44925</v>
-      </c>
-      <c r="I22" s="56">
-        <f>NETWORKDAYS(G22,H22)</f>
-        <v>11</v>
-      </c>
-      <c r="J22" s="50"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O22" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P22" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q22" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R22" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S22" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T22" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U22" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V22" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W22" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X22" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y22" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z22" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA22" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB22" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC22" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD22" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE22" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF22" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG22" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH22" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI22" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ22" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK22" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL22" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM22" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN22" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO22" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP22" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ22" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR22" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS22" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT22" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU22" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV22" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW22" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX22" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY22" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ22" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA22" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB22" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC22" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD22" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE22" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF22" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG22" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH22" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI22" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ22" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK22" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL22" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM22" s="90">
-        <v>44922</v>
-      </c>
+    <row r="22" spans="1:66" ht="69" customHeight="1">
+      <c r="F22" s="63"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="48"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="68"/>
+      <c r="U22" s="69"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="75"/>
+      <c r="AE22" s="76"/>
+      <c r="AF22" s="77"/>
+      <c r="AG22" s="78"/>
+      <c r="AH22" s="79"/>
+      <c r="AI22" s="80"/>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="81"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="83"/>
+      <c r="AN22" s="72"/>
+      <c r="AO22" s="73"/>
+      <c r="AP22" s="74"/>
+      <c r="AQ22" s="94"/>
+      <c r="AR22" s="95"/>
+      <c r="AS22" s="84"/>
+      <c r="AT22" s="85"/>
+      <c r="AU22" s="96"/>
+      <c r="AV22" s="106"/>
+      <c r="AW22" s="86"/>
+      <c r="AX22" s="5"/>
+      <c r="AY22" s="87"/>
+      <c r="AZ22" s="88"/>
+      <c r="BA22" s="8"/>
+      <c r="BB22" s="5"/>
+      <c r="BC22" s="65"/>
+      <c r="BD22" s="109"/>
+      <c r="BE22" s="111"/>
+      <c r="BF22" s="67"/>
+      <c r="BG22" s="68"/>
+      <c r="BH22" s="108"/>
+      <c r="BI22" s="112"/>
+      <c r="BJ22" s="86"/>
+      <c r="BK22" s="89"/>
+      <c r="BL22" s="87"/>
+      <c r="BM22" s="90"/>
       <c r="BN22" s="11"/>
     </row>
-    <row r="23" spans="1:66" ht="25.25" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="42">
-        <v>7.1</v>
-      </c>
-      <c r="F23" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="52">
-        <v>44911</v>
-      </c>
-      <c r="H23" s="52">
-        <v>44919</v>
-      </c>
-      <c r="I23" s="53">
-        <f>NETWORKDAYS(G23,H23)</f>
-        <v>6</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="54">
-        <v>3</v>
-      </c>
-      <c r="L23" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="N23" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O23" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P23" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q23" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R23" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S23" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T23" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U23" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V23" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W23" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X23" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y23" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z23" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA23" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB23" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC23" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD23" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE23" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF23" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG23" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH23" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI23" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ23" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK23" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL23" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM23" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN23" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO23" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP23" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ23" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR23" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS23" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT23" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU23" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV23" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW23" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX23" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY23" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ23" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA23" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB23" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC23" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD23" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE23" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF23" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG23" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH23" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI23" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ23" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK23" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL23" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM23" s="90">
-        <v>44922</v>
-      </c>
+    <row r="23" spans="1:66" ht="69" customHeight="1">
+      <c r="F23" s="63"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="71"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="73"/>
+      <c r="AC23" s="74"/>
+      <c r="AD23" s="75"/>
+      <c r="AE23" s="76"/>
+      <c r="AF23" s="77"/>
+      <c r="AG23" s="78"/>
+      <c r="AH23" s="79"/>
+      <c r="AI23" s="80"/>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="81"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="83"/>
+      <c r="AN23" s="72"/>
+      <c r="AO23" s="73"/>
+      <c r="AP23" s="74"/>
+      <c r="AQ23" s="94"/>
+      <c r="AR23" s="95"/>
+      <c r="AS23" s="84"/>
+      <c r="AT23" s="85"/>
+      <c r="AU23" s="96"/>
+      <c r="AV23" s="106"/>
+      <c r="AW23" s="86"/>
+      <c r="AX23" s="5"/>
+      <c r="AY23" s="87"/>
+      <c r="AZ23" s="88"/>
+      <c r="BA23" s="8"/>
+      <c r="BB23" s="5"/>
+      <c r="BC23" s="65"/>
+      <c r="BD23" s="109"/>
+      <c r="BE23" s="111"/>
+      <c r="BF23" s="67"/>
+      <c r="BG23" s="68"/>
+      <c r="BH23" s="108"/>
+      <c r="BI23" s="112"/>
+      <c r="BJ23" s="86"/>
+      <c r="BK23" s="89"/>
+      <c r="BL23" s="87"/>
+      <c r="BM23" s="90"/>
       <c r="BN23" s="11"/>
     </row>
-    <row r="24" spans="1:66" ht="25.25" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="42">
-        <v>7.2</v>
-      </c>
-      <c r="F24" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="52">
-        <v>44917</v>
-      </c>
-      <c r="H24" s="52">
-        <v>44925</v>
-      </c>
-      <c r="I24" s="53">
-        <f t="shared" ref="I24" si="6">NETWORKDAYS(G24,H24)</f>
-        <v>7</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="K24" s="54">
-        <v>2</v>
-      </c>
-      <c r="L24" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="M24" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="N24" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O24" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P24" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q24" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R24" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S24" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T24" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U24" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V24" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W24" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X24" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y24" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z24" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA24" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB24" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC24" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD24" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE24" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF24" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG24" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH24" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI24" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ24" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK24" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL24" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM24" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN24" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO24" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP24" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ24" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR24" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS24" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT24" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU24" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV24" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW24" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX24" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY24" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ24" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA24" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB24" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC24" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD24" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE24" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF24" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG24" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH24" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI24" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ24" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK24" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL24" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM24" s="90">
-        <v>44922</v>
-      </c>
+    <row r="24" spans="1:66" ht="69" customHeight="1">
+      <c r="F24" s="63"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="48"/>
+      <c r="M24" s="60"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="68"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="71"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="73"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="75"/>
+      <c r="AE24" s="76"/>
+      <c r="AF24" s="77"/>
+      <c r="AG24" s="78"/>
+      <c r="AH24" s="79"/>
+      <c r="AI24" s="80"/>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="81"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="83"/>
+      <c r="AN24" s="72"/>
+      <c r="AO24" s="73"/>
+      <c r="AP24" s="74"/>
+      <c r="AQ24" s="94"/>
+      <c r="AR24" s="95"/>
+      <c r="AS24" s="84"/>
+      <c r="AT24" s="85"/>
+      <c r="AU24" s="96"/>
+      <c r="AV24" s="106"/>
+      <c r="AW24" s="86"/>
+      <c r="AX24" s="5"/>
+      <c r="AY24" s="87"/>
+      <c r="AZ24" s="88"/>
+      <c r="BA24" s="8"/>
+      <c r="BB24" s="5"/>
+      <c r="BC24" s="65"/>
+      <c r="BD24" s="109"/>
+      <c r="BE24" s="111"/>
+      <c r="BF24" s="67"/>
+      <c r="BG24" s="68"/>
+      <c r="BH24" s="108"/>
+      <c r="BI24" s="112"/>
+      <c r="BJ24" s="86"/>
+      <c r="BK24" s="89"/>
+      <c r="BL24" s="87"/>
+      <c r="BM24" s="90"/>
       <c r="BN24" s="11"/>
     </row>
-    <row r="25" spans="1:66" ht="15.5" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="40">
-        <v>8</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="55">
-        <v>44911</v>
-      </c>
-      <c r="H25" s="55">
-        <v>44925</v>
-      </c>
-      <c r="I25" s="56">
-        <f>NETWORKDAYS(G25,H25)</f>
-        <v>11</v>
-      </c>
-      <c r="J25" s="50"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O25" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P25" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q25" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R25" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S25" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T25" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U25" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V25" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W25" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X25" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y25" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z25" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA25" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB25" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC25" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD25" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE25" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF25" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG25" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH25" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI25" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ25" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK25" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL25" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM25" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN25" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO25" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP25" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ25" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR25" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS25" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT25" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU25" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV25" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW25" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX25" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY25" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ25" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA25" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB25" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC25" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD25" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE25" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF25" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG25" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH25" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI25" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ25" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK25" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL25" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM25" s="90">
-        <v>44922</v>
-      </c>
+    <row r="25" spans="1:66" ht="69" customHeight="1">
+      <c r="F25" s="63"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="48"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="68"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="68"/>
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="71"/>
+      <c r="AA25" s="72"/>
+      <c r="AB25" s="73"/>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="75"/>
+      <c r="AE25" s="76"/>
+      <c r="AF25" s="77"/>
+      <c r="AG25" s="78"/>
+      <c r="AH25" s="79"/>
+      <c r="AI25" s="80"/>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="81"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="83"/>
+      <c r="AN25" s="72"/>
+      <c r="AO25" s="73"/>
+      <c r="AP25" s="74"/>
+      <c r="AQ25" s="94"/>
+      <c r="AR25" s="95"/>
+      <c r="AS25" s="84"/>
+      <c r="AT25" s="85"/>
+      <c r="AU25" s="96"/>
+      <c r="AV25" s="106"/>
+      <c r="AW25" s="86"/>
+      <c r="AX25" s="5"/>
+      <c r="AY25" s="87"/>
+      <c r="AZ25" s="88"/>
+      <c r="BA25" s="8"/>
+      <c r="BB25" s="5"/>
+      <c r="BC25" s="65"/>
+      <c r="BD25" s="109"/>
+      <c r="BE25" s="111"/>
+      <c r="BF25" s="67"/>
+      <c r="BG25" s="68"/>
+      <c r="BH25" s="108"/>
+      <c r="BI25" s="112"/>
+      <c r="BJ25" s="86"/>
+      <c r="BK25" s="89"/>
+      <c r="BL25" s="87"/>
+      <c r="BM25" s="90"/>
       <c r="BN25" s="11"/>
     </row>
-    <row r="26" spans="1:66" ht="51.5" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="42">
-        <v>8.1</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26" s="52">
-        <v>44911</v>
-      </c>
-      <c r="H26" s="52">
-        <v>44925</v>
-      </c>
-      <c r="I26" s="53">
-        <f t="shared" ref="I26" si="7">NETWORKDAYS(G26,H26)</f>
-        <v>11</v>
-      </c>
-      <c r="J26" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" s="54">
-        <v>2</v>
-      </c>
-      <c r="L26" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="M26" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="N26" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O26" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P26" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q26" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R26" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S26" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T26" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U26" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V26" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W26" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X26" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y26" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z26" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA26" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB26" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC26" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD26" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE26" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF26" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG26" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH26" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI26" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ26" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK26" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL26" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM26" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN26" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO26" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP26" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ26" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR26" s="95">
-        <v>44775</v>
-      </c>
-      <c r="AS26" s="84">
-        <v>44782</v>
-      </c>
-      <c r="AT26" s="85">
-        <v>44789</v>
-      </c>
-      <c r="AU26" s="96">
-        <v>44796</v>
-      </c>
-      <c r="AV26" s="106">
-        <v>44803</v>
-      </c>
-      <c r="AW26" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX26" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY26" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ26" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA26" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB26" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC26" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD26" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE26" s="111">
-        <v>44866</v>
-      </c>
-      <c r="BF26" s="67">
-        <v>44873</v>
-      </c>
-      <c r="BG26" s="68">
-        <v>44880</v>
-      </c>
-      <c r="BH26" s="108">
-        <v>44887</v>
-      </c>
-      <c r="BI26" s="112">
-        <v>44894</v>
-      </c>
-      <c r="BJ26" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK26" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL26" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM26" s="90">
-        <v>44922</v>
-      </c>
+    <row r="26" spans="1:66" ht="102.5" customHeight="1">
+      <c r="F26" s="63"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="48"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="69"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="70"/>
+      <c r="Z26" s="71"/>
+      <c r="AA26" s="72"/>
+      <c r="AB26" s="73"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="75"/>
+      <c r="AE26" s="76"/>
+      <c r="AF26" s="77"/>
+      <c r="AG26" s="78"/>
+      <c r="AH26" s="79"/>
+      <c r="AI26" s="80"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="81"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="83"/>
+      <c r="AN26" s="72"/>
+      <c r="AO26" s="73"/>
+      <c r="AP26" s="74"/>
+      <c r="AQ26" s="94"/>
+      <c r="AR26" s="95"/>
+      <c r="AS26" s="84"/>
+      <c r="AT26" s="85"/>
+      <c r="AU26" s="96"/>
+      <c r="AV26" s="106"/>
+      <c r="AW26" s="86"/>
+      <c r="AX26" s="5"/>
+      <c r="AY26" s="87"/>
+      <c r="AZ26" s="88"/>
+      <c r="BA26" s="8"/>
+      <c r="BB26" s="5"/>
+      <c r="BC26" s="65"/>
+      <c r="BD26" s="109"/>
+      <c r="BE26" s="111"/>
+      <c r="BF26" s="67"/>
+      <c r="BG26" s="68"/>
+      <c r="BH26" s="108"/>
+      <c r="BI26" s="112"/>
+      <c r="BJ26" s="86"/>
+      <c r="BK26" s="89"/>
+      <c r="BL26" s="87"/>
+      <c r="BM26" s="90"/>
       <c r="BN26" s="11"/>
     </row>
-    <row r="27" spans="1:66" ht="53.5" customHeight="1">
-      <c r="E27" s="62">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F27" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="52">
-        <v>44920</v>
-      </c>
-      <c r="H27" s="52">
-        <v>44925</v>
-      </c>
-      <c r="I27" s="53">
-        <f t="shared" ref="I27" si="8">NETWORKDAYS(G27,H27)</f>
-        <v>5</v>
-      </c>
-      <c r="J27" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="K27" s="54">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N27" s="5">
-        <v>44564</v>
-      </c>
-      <c r="O27" s="64">
-        <v>44572</v>
-      </c>
-      <c r="P27" s="65">
-        <v>44579</v>
-      </c>
-      <c r="Q27" s="66">
-        <v>44586</v>
-      </c>
-      <c r="R27" s="5">
-        <v>44593</v>
-      </c>
-      <c r="S27" s="67">
-        <v>44600</v>
-      </c>
-      <c r="T27" s="68">
-        <v>44607</v>
-      </c>
-      <c r="U27" s="69">
-        <v>44614</v>
-      </c>
-      <c r="V27" s="5">
-        <v>44621</v>
-      </c>
-      <c r="W27" s="67">
-        <v>44628</v>
-      </c>
-      <c r="X27" s="68">
-        <v>44635</v>
-      </c>
-      <c r="Y27" s="70">
-        <v>44642</v>
-      </c>
-      <c r="Z27" s="71">
-        <v>44649</v>
-      </c>
-      <c r="AA27" s="72">
-        <v>44656</v>
-      </c>
-      <c r="AB27" s="73">
-        <v>44663</v>
-      </c>
-      <c r="AC27" s="74">
-        <v>44670</v>
-      </c>
-      <c r="AD27" s="75">
-        <v>44677</v>
-      </c>
-      <c r="AE27" s="76">
-        <v>44684</v>
-      </c>
-      <c r="AF27" s="77">
-        <v>44691</v>
-      </c>
-      <c r="AG27" s="78">
-        <v>44698</v>
-      </c>
-      <c r="AH27" s="79">
-        <v>44705</v>
-      </c>
-      <c r="AI27" s="80">
-        <v>44712</v>
-      </c>
-      <c r="AJ27" s="5">
-        <v>44719</v>
-      </c>
-      <c r="AK27" s="81">
-        <v>44726</v>
-      </c>
-      <c r="AL27" s="82">
-        <v>44733</v>
-      </c>
-      <c r="AM27" s="83">
-        <v>44740</v>
-      </c>
-      <c r="AN27" s="72">
-        <v>44747</v>
-      </c>
-      <c r="AO27" s="73">
-        <v>44754</v>
-      </c>
-      <c r="AP27" s="74">
-        <v>44761</v>
-      </c>
-      <c r="AQ27" s="94">
-        <v>44768</v>
-      </c>
-      <c r="AR27" s="97">
-        <v>44775</v>
-      </c>
-      <c r="AS27" s="98">
-        <v>44782</v>
-      </c>
-      <c r="AT27" s="99">
-        <v>44789</v>
-      </c>
-      <c r="AU27" s="100">
-        <v>44796</v>
-      </c>
-      <c r="AV27" s="107">
-        <v>44803</v>
-      </c>
-      <c r="AW27" s="86">
-        <v>44810</v>
-      </c>
-      <c r="AX27" s="5">
-        <v>44817</v>
-      </c>
-      <c r="AY27" s="87">
-        <v>44824</v>
-      </c>
-      <c r="AZ27" s="88">
-        <v>44831</v>
-      </c>
-      <c r="BA27" s="8">
-        <v>44838</v>
-      </c>
-      <c r="BB27" s="5">
-        <v>44845</v>
-      </c>
-      <c r="BC27" s="65">
-        <v>44852</v>
-      </c>
-      <c r="BD27" s="109">
-        <v>44859</v>
-      </c>
-      <c r="BE27" s="113">
-        <v>44866</v>
-      </c>
-      <c r="BF27" s="114">
-        <v>44873</v>
-      </c>
-      <c r="BG27" s="115">
-        <v>44880</v>
-      </c>
-      <c r="BH27" s="116">
-        <v>44887</v>
-      </c>
-      <c r="BI27" s="117">
-        <v>44894</v>
-      </c>
-      <c r="BJ27" s="86">
-        <v>44901</v>
-      </c>
-      <c r="BK27" s="89">
-        <v>44908</v>
-      </c>
-      <c r="BL27" s="87">
-        <v>44915</v>
-      </c>
-      <c r="BM27" s="90">
-        <v>44922</v>
-      </c>
+    <row r="27" spans="1:66" ht="15.5" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="68"/>
+      <c r="U27" s="69"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="68"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="71"/>
+      <c r="AA27" s="72"/>
+      <c r="AB27" s="73"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="77"/>
+      <c r="AG27" s="78"/>
+      <c r="AH27" s="79"/>
+      <c r="AI27" s="80"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="81"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="83"/>
+      <c r="AN27" s="72"/>
+      <c r="AO27" s="73"/>
+      <c r="AP27" s="74"/>
+      <c r="AQ27" s="94"/>
+      <c r="AR27" s="95"/>
+      <c r="AS27" s="84"/>
+      <c r="AT27" s="85"/>
+      <c r="AU27" s="96"/>
+      <c r="AV27" s="106"/>
+      <c r="AW27" s="86"/>
+      <c r="AX27" s="5"/>
+      <c r="AY27" s="87"/>
+      <c r="AZ27" s="88"/>
+      <c r="BA27" s="8"/>
+      <c r="BB27" s="5"/>
+      <c r="BC27" s="65"/>
+      <c r="BD27" s="109"/>
+      <c r="BE27" s="111"/>
+      <c r="BF27" s="67"/>
+      <c r="BG27" s="68"/>
+      <c r="BH27" s="108"/>
+      <c r="BI27" s="112"/>
+      <c r="BJ27" s="86"/>
+      <c r="BK27" s="89"/>
+      <c r="BL27" s="87"/>
+      <c r="BM27" s="90"/>
       <c r="BN27" s="11"/>
     </row>
-    <row r="32" spans="1:66">
-      <c r="J32" s="49" t="s">
+    <row r="28" spans="1:66" ht="63" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="71"/>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="73"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="75"/>
+      <c r="AE28" s="76"/>
+      <c r="AF28" s="77"/>
+      <c r="AG28" s="78"/>
+      <c r="AH28" s="79"/>
+      <c r="AI28" s="80"/>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="81"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="83"/>
+      <c r="AN28" s="72"/>
+      <c r="AO28" s="73"/>
+      <c r="AP28" s="74"/>
+      <c r="AQ28" s="94"/>
+      <c r="AR28" s="95"/>
+      <c r="AS28" s="84"/>
+      <c r="AT28" s="85"/>
+      <c r="AU28" s="96"/>
+      <c r="AV28" s="106"/>
+      <c r="AW28" s="86"/>
+      <c r="AX28" s="5"/>
+      <c r="AY28" s="87"/>
+      <c r="AZ28" s="88"/>
+      <c r="BA28" s="8"/>
+      <c r="BB28" s="5"/>
+      <c r="BC28" s="65"/>
+      <c r="BD28" s="109"/>
+      <c r="BE28" s="111"/>
+      <c r="BF28" s="67"/>
+      <c r="BG28" s="68"/>
+      <c r="BH28" s="108"/>
+      <c r="BI28" s="112"/>
+      <c r="BJ28" s="86"/>
+      <c r="BK28" s="89"/>
+      <c r="BL28" s="87"/>
+      <c r="BM28" s="90"/>
+      <c r="BN28" s="11"/>
+    </row>
+    <row r="29" spans="1:66" ht="15.5" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="69"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="71"/>
+      <c r="AA29" s="72"/>
+      <c r="AB29" s="73"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="75"/>
+      <c r="AE29" s="76"/>
+      <c r="AF29" s="77"/>
+      <c r="AG29" s="78"/>
+      <c r="AH29" s="79"/>
+      <c r="AI29" s="80"/>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="81"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="83"/>
+      <c r="AN29" s="72"/>
+      <c r="AO29" s="73"/>
+      <c r="AP29" s="74"/>
+      <c r="AQ29" s="94"/>
+      <c r="AR29" s="95"/>
+      <c r="AS29" s="84"/>
+      <c r="AT29" s="85"/>
+      <c r="AU29" s="96"/>
+      <c r="AV29" s="106"/>
+      <c r="AW29" s="86"/>
+      <c r="AX29" s="5"/>
+      <c r="AY29" s="87"/>
+      <c r="AZ29" s="88"/>
+      <c r="BA29" s="8"/>
+      <c r="BB29" s="5"/>
+      <c r="BC29" s="65"/>
+      <c r="BD29" s="109"/>
+      <c r="BE29" s="111"/>
+      <c r="BF29" s="67"/>
+      <c r="BG29" s="68"/>
+      <c r="BH29" s="108"/>
+      <c r="BI29" s="112"/>
+      <c r="BJ29" s="86"/>
+      <c r="BK29" s="89"/>
+      <c r="BL29" s="87"/>
+      <c r="BM29" s="90"/>
+      <c r="BN29" s="11"/>
+    </row>
+    <row r="30" spans="1:66" ht="25.25" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="68"/>
+      <c r="U30" s="69"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="70"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="72"/>
+      <c r="AB30" s="73"/>
+      <c r="AC30" s="74"/>
+      <c r="AD30" s="75"/>
+      <c r="AE30" s="76"/>
+      <c r="AF30" s="77"/>
+      <c r="AG30" s="78"/>
+      <c r="AH30" s="79"/>
+      <c r="AI30" s="80"/>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="81"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="83"/>
+      <c r="AN30" s="72"/>
+      <c r="AO30" s="73"/>
+      <c r="AP30" s="74"/>
+      <c r="AQ30" s="94"/>
+      <c r="AR30" s="95"/>
+      <c r="AS30" s="84"/>
+      <c r="AT30" s="85"/>
+      <c r="AU30" s="96"/>
+      <c r="AV30" s="106"/>
+      <c r="AW30" s="86"/>
+      <c r="AX30" s="5"/>
+      <c r="AY30" s="87"/>
+      <c r="AZ30" s="88"/>
+      <c r="BA30" s="8"/>
+      <c r="BB30" s="5"/>
+      <c r="BC30" s="65"/>
+      <c r="BD30" s="109"/>
+      <c r="BE30" s="111"/>
+      <c r="BF30" s="67"/>
+      <c r="BG30" s="68"/>
+      <c r="BH30" s="108"/>
+      <c r="BI30" s="112"/>
+      <c r="BJ30" s="86"/>
+      <c r="BK30" s="89"/>
+      <c r="BL30" s="87"/>
+      <c r="BM30" s="90"/>
+      <c r="BN30" s="11"/>
+    </row>
+    <row r="31" spans="1:66" ht="25.25" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="68"/>
+      <c r="U31" s="69"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="68"/>
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="71"/>
+      <c r="AA31" s="72"/>
+      <c r="AB31" s="73"/>
+      <c r="AC31" s="74"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="77"/>
+      <c r="AG31" s="78"/>
+      <c r="AH31" s="79"/>
+      <c r="AI31" s="80"/>
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="81"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="83"/>
+      <c r="AN31" s="72"/>
+      <c r="AO31" s="73"/>
+      <c r="AP31" s="74"/>
+      <c r="AQ31" s="94"/>
+      <c r="AR31" s="95"/>
+      <c r="AS31" s="84"/>
+      <c r="AT31" s="85"/>
+      <c r="AU31" s="96"/>
+      <c r="AV31" s="106"/>
+      <c r="AW31" s="86"/>
+      <c r="AX31" s="5"/>
+      <c r="AY31" s="87"/>
+      <c r="AZ31" s="88"/>
+      <c r="BA31" s="8"/>
+      <c r="BB31" s="5"/>
+      <c r="BC31" s="65"/>
+      <c r="BD31" s="109"/>
+      <c r="BE31" s="111"/>
+      <c r="BF31" s="67"/>
+      <c r="BG31" s="68"/>
+      <c r="BH31" s="108"/>
+      <c r="BI31" s="112"/>
+      <c r="BJ31" s="86"/>
+      <c r="BK31" s="89"/>
+      <c r="BL31" s="87"/>
+      <c r="BM31" s="90"/>
+      <c r="BN31" s="11"/>
+    </row>
+    <row r="32" spans="1:66" ht="15.5" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="69"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="70"/>
+      <c r="Z32" s="71"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="73"/>
+      <c r="AC32" s="74"/>
+      <c r="AD32" s="75"/>
+      <c r="AE32" s="76"/>
+      <c r="AF32" s="77"/>
+      <c r="AG32" s="78"/>
+      <c r="AH32" s="79"/>
+      <c r="AI32" s="80"/>
+      <c r="AJ32" s="5"/>
+      <c r="AK32" s="81"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="83"/>
+      <c r="AN32" s="72"/>
+      <c r="AO32" s="73"/>
+      <c r="AP32" s="74"/>
+      <c r="AQ32" s="94"/>
+      <c r="AR32" s="95"/>
+      <c r="AS32" s="84"/>
+      <c r="AT32" s="85"/>
+      <c r="AU32" s="96"/>
+      <c r="AV32" s="106"/>
+      <c r="AW32" s="86"/>
+      <c r="AX32" s="5"/>
+      <c r="AY32" s="87"/>
+      <c r="AZ32" s="88"/>
+      <c r="BA32" s="8"/>
+      <c r="BB32" s="5"/>
+      <c r="BC32" s="65"/>
+      <c r="BD32" s="109"/>
+      <c r="BE32" s="111"/>
+      <c r="BF32" s="67"/>
+      <c r="BG32" s="68"/>
+      <c r="BH32" s="108"/>
+      <c r="BI32" s="112"/>
+      <c r="BJ32" s="86"/>
+      <c r="BK32" s="89"/>
+      <c r="BL32" s="87"/>
+      <c r="BM32" s="90"/>
+      <c r="BN32" s="11"/>
+    </row>
+    <row r="33" spans="1:66" ht="51.5" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="68"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="68"/>
+      <c r="Y33" s="70"/>
+      <c r="Z33" s="71"/>
+      <c r="AA33" s="72"/>
+      <c r="AB33" s="73"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="75"/>
+      <c r="AE33" s="76"/>
+      <c r="AF33" s="77"/>
+      <c r="AG33" s="78"/>
+      <c r="AH33" s="79"/>
+      <c r="AI33" s="80"/>
+      <c r="AJ33" s="5"/>
+      <c r="AK33" s="81"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="83"/>
+      <c r="AN33" s="72"/>
+      <c r="AO33" s="73"/>
+      <c r="AP33" s="74"/>
+      <c r="AQ33" s="94"/>
+      <c r="AR33" s="95"/>
+      <c r="AS33" s="84"/>
+      <c r="AT33" s="85"/>
+      <c r="AU33" s="96"/>
+      <c r="AV33" s="106"/>
+      <c r="AW33" s="86"/>
+      <c r="AX33" s="5"/>
+      <c r="AY33" s="87"/>
+      <c r="AZ33" s="88"/>
+      <c r="BA33" s="8"/>
+      <c r="BB33" s="5"/>
+      <c r="BC33" s="65"/>
+      <c r="BD33" s="109"/>
+      <c r="BE33" s="111"/>
+      <c r="BF33" s="67"/>
+      <c r="BG33" s="68"/>
+      <c r="BH33" s="108"/>
+      <c r="BI33" s="112"/>
+      <c r="BJ33" s="86"/>
+      <c r="BK33" s="89"/>
+      <c r="BL33" s="87"/>
+      <c r="BM33" s="90"/>
+      <c r="BN33" s="11"/>
+    </row>
+    <row r="34" spans="1:66" ht="53.5" customHeight="1">
+      <c r="F34" s="63"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="54"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="68"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="71"/>
+      <c r="AA34" s="72"/>
+      <c r="AB34" s="73"/>
+      <c r="AC34" s="74"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="77"/>
+      <c r="AG34" s="78"/>
+      <c r="AH34" s="79"/>
+      <c r="AI34" s="80"/>
+      <c r="AJ34" s="5"/>
+      <c r="AK34" s="81"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="83"/>
+      <c r="AN34" s="72"/>
+      <c r="AO34" s="73"/>
+      <c r="AP34" s="74"/>
+      <c r="AQ34" s="94"/>
+      <c r="AR34" s="97"/>
+      <c r="AS34" s="98"/>
+      <c r="AT34" s="99"/>
+      <c r="AU34" s="100"/>
+      <c r="AV34" s="107"/>
+      <c r="AW34" s="86"/>
+      <c r="AX34" s="5"/>
+      <c r="AY34" s="87"/>
+      <c r="AZ34" s="88"/>
+      <c r="BA34" s="8"/>
+      <c r="BB34" s="5"/>
+      <c r="BC34" s="65"/>
+      <c r="BD34" s="109"/>
+      <c r="BE34" s="113"/>
+      <c r="BF34" s="114"/>
+      <c r="BG34" s="115"/>
+      <c r="BH34" s="116"/>
+      <c r="BI34" s="117"/>
+      <c r="BJ34" s="86"/>
+      <c r="BK34" s="89"/>
+      <c r="BL34" s="87"/>
+      <c r="BM34" s="90"/>
+      <c r="BN34" s="11"/>
+    </row>
+    <row r="37" spans="1:66">
+      <c r="J37" s="49" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="10:10">
-      <c r="J33" s="49" t="s">
+    <row r="38" spans="1:66">
+      <c r="J38" s="49" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="10:10">
-      <c r="J34" s="49" t="s">
+    <row r="39" spans="1:66">
+      <c r="J39" s="49" t="s">
         <v>77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AN4:AQ4"/>
-    <mergeCell ref="AE4:AI4"/>
-    <mergeCell ref="AJ4:AM4"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:F5"/>
-    <mergeCell ref="G3:I4"/>
-    <mergeCell ref="J3:J5"/>
     <mergeCell ref="BN3:BN5"/>
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="R4:U4"/>
@@ -7640,98 +6859,146 @@
     <mergeCell ref="AR4:AV4"/>
     <mergeCell ref="BE4:BI4"/>
     <mergeCell ref="BJ4:BM4"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:F5"/>
+    <mergeCell ref="G3:I4"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AN4:AQ4"/>
+    <mergeCell ref="AE4:AI4"/>
+    <mergeCell ref="AJ4:AM4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J7:J14 J20:J27">
-    <cfRule type="cellIs" dxfId="4" priority="45" operator="equal">
+  <conditionalFormatting sqref="J7:J16">
+    <cfRule type="cellIs" dxfId="25" priority="14" operator="equal">
       <formula>"지연중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="15" operator="equal">
       <formula>"진행중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="16" operator="equal">
       <formula>"완료"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="cellIs" dxfId="21" priority="37" operator="equal">
+  <conditionalFormatting sqref="J21:J24">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+      <formula>"진행중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+      <formula>"완료"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"지연중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="38" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26:J34">
+    <cfRule type="cellIs" dxfId="19" priority="131" operator="equal">
+      <formula>"완료"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="130" operator="equal">
       <formula>"진행중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="129" operator="equal">
+      <formula>"지연중"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37:J39">
+    <cfRule type="cellIs" dxfId="16" priority="85" operator="equal">
+      <formula>"지연중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="87" operator="equal">
       <formula>"완료"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
-    <cfRule type="cellIs" dxfId="18" priority="29" operator="equal">
-      <formula>"지연중"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="86" operator="equal">
       <formula>"진행중"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="31" operator="equal">
-      <formula>"완료"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:BM6">
-    <cfRule type="cellIs" dxfId="15" priority="179" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="263" operator="between">
       <formula>$G6</formula>
       <formula>$H6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:BM7 N12:BM12 N22:BM22 N25:BM25">
-    <cfRule type="cellIs" dxfId="14" priority="180" operator="between">
+  <conditionalFormatting sqref="N7:BM7">
+    <cfRule type="cellIs" dxfId="12" priority="264" operator="between">
       <formula>$G7</formula>
       <formula>$H7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:BM11 N13:BM13 N15:BM15 N21:BM21">
-    <cfRule type="cellIs" dxfId="13" priority="83" operator="between">
+  <conditionalFormatting sqref="N8:BM9 N11:BM11">
+    <cfRule type="cellIs" dxfId="11" priority="167" operator="between">
       <formula>$G8</formula>
       <formula>$H8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N14:BM14">
-    <cfRule type="cellIs" dxfId="12" priority="48" operator="between">
-      <formula>$G14</formula>
-      <formula>$H14</formula>
+  <conditionalFormatting sqref="N10:BM10">
+    <cfRule type="cellIs" dxfId="10" priority="132" operator="between">
+      <formula>$G10</formula>
+      <formula>$H10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N17:BM17 N19:BM19 N23:BM24 N26:BM27">
-    <cfRule type="cellIs" dxfId="11" priority="181" operator="between">
+  <conditionalFormatting sqref="N12:BM12">
+    <cfRule type="cellIs" dxfId="9" priority="42" operator="between">
+      <formula>$G12</formula>
+      <formula>$H12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:BM15">
+    <cfRule type="cellIs" dxfId="8" priority="33" operator="between">
+      <formula>$G13</formula>
+      <formula>$H13</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N16:BM16">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="between">
+      <formula>$G16</formula>
+      <formula>$H16</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21:BM21">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="between">
+      <formula>$G21</formula>
+      <formula>$H21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22:BM25">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+      <formula>$G22</formula>
+      <formula>$H22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22:BM26 N17:BM20 N28:BM28">
+    <cfRule type="cellIs" dxfId="4" priority="83" operator="between">
       <formula>$G17</formula>
       <formula>$H17</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N16:BM16">
-    <cfRule type="cellIs" dxfId="10" priority="40" operator="between">
-      <formula>$G16</formula>
-      <formula>$H16</formula>
+  <conditionalFormatting sqref="N23:BM23">
+    <cfRule type="cellIs" dxfId="3" priority="24" operator="between">
+      <formula>$G23</formula>
+      <formula>$H23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:BM18">
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="between">
-      <formula>$G18</formula>
-      <formula>$H18</formula>
+  <conditionalFormatting sqref="N27:BM27">
+    <cfRule type="cellIs" dxfId="2" priority="73" operator="between">
+      <formula>$G27</formula>
+      <formula>$H27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N20:BM20">
-    <cfRule type="cellIs" dxfId="8" priority="24" operator="between">
-      <formula>$G20</formula>
-      <formula>$H20</formula>
+  <conditionalFormatting sqref="N28:BM34">
+    <cfRule type="cellIs" dxfId="1" priority="265" operator="between">
+      <formula>$G28</formula>
+      <formula>$H28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J32:J34">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
-      <formula>"지연중"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
-      <formula>"진행중"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
-      <formula>"완료"</formula>
+  <conditionalFormatting sqref="N29:BM30 N32:BM32">
+    <cfRule type="cellIs" dxfId="0" priority="84" operator="between">
+      <formula>$G29</formula>
+      <formula>$H29</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
